--- a/data dictionary/insect_egg_metadata.xlsx
+++ b/data dictionary/insect_egg_metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ueanorwich-my.sharepoint.com/personal/hpd08ucu_uea_ac_uk/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phill\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC107BE9-9FD2-4D03-9D5D-B1ABE61CA6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F7B84F-73C1-4C13-A884-06B1EE84D901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4965" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7C55039F-DCE7-4CD6-AE49-F8EF1822AE98}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7C55039F-DCE7-4CD6-AE49-F8EF1822AE98}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
   <si>
     <t>Type</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Integer</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>Unique identifier for each female insect.</t>
   </si>
   <si>
@@ -449,6 +446,42 @@
   </si>
   <si>
     <t>p.leftwich@ueac.uk</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Date egg collections made</t>
+  </si>
+  <si>
+    <t>treatment</t>
+  </si>
+  <si>
+    <t>Treatment applied to experimental cages</t>
+  </si>
+  <si>
+    <t>Character</t>
+  </si>
+  <si>
+    <t>Character string applied to columns</t>
+  </si>
+  <si>
+    <t>Character strings [A-Z]</t>
+  </si>
+  <si>
+    <t>"A", "B"</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>dmy date format</t>
+  </si>
+  <si>
+    <t>Date firsrt egg collection made from cages</t>
+  </si>
+  <si>
+    <t>Dates between 1/10/25 and 31/10/25</t>
   </si>
 </sst>
 </file>
@@ -507,7 +540,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -526,6 +559,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -863,10 +899,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A579486B-6E4E-47C2-8304-E142B8B40C67}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="14.7265625" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" customWidth="1"/>
     <col min="4" max="4" width="16.26953125" customWidth="1"/>
     <col min="5" max="5" width="14.90625" customWidth="1"/>
     <col min="6" max="7" width="21.7265625" customWidth="1"/>
@@ -876,10 +913,10 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -894,13 +931,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -908,124 +945,156 @@
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
+    </row>
+    <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="8">
+        <v>45940</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
@@ -1046,6 +1115,16 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1064,7 +1143,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -1075,13 +1154,13 @@
     </row>
     <row r="2" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="145" x14ac:dyDescent="0.35">
@@ -1089,120 +1168,120 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="C8" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="C9" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="C11" s="7">
         <v>45950</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
